--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-EX-EU-IS-REDEEMABLE-BY-PROPERTIES.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-EX-EU-IS-REDEEMABLE-BY-PROPERTIES.xlsx
@@ -1353,7 +1353,7 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>109</v>

--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-EX-EU-IS-REDEEMABLE-BY-PROPERTIES.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-EX-EU-IS-REDEEMABLE-BY-PROPERTIES.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
